--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I490"/>
+  <dimension ref="A1:I491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16606,6 +16606,39 @@
         <v>383.24</v>
       </c>
       <c r="I490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="C491" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="D491" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="E491" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="F491" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="G491" t="n">
+        <v>388.04</v>
+      </c>
+      <c r="H491" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="I491" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16622,7 +16655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22165,6 +22198,16 @@
       </c>
       <c r="B554" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -22333,28 +22376,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2067179876628555</v>
+        <v>0.2036220473045119</v>
       </c>
       <c r="J2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K2" t="n">
         <v>489</v>
       </c>
-      <c r="K2" t="n">
-        <v>488</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01256058956577144</v>
+        <v>0.01223345460837011</v>
       </c>
       <c r="M2" t="n">
-        <v>11.03602581597689</v>
+        <v>11.03002191486912</v>
       </c>
       <c r="N2" t="n">
-        <v>196.5210540562135</v>
+        <v>196.2543521937775</v>
       </c>
       <c r="O2" t="n">
-        <v>14.01859672207648</v>
+        <v>14.0090810617177</v>
       </c>
       <c r="P2" t="n">
-        <v>394.835344356642</v>
+        <v>394.866475099992</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22411,28 +22454,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07198395427395175</v>
+        <v>0.0694821270358887</v>
       </c>
       <c r="J3" t="n">
+        <v>490</v>
+      </c>
+      <c r="K3" t="n">
         <v>489</v>
       </c>
-      <c r="K3" t="n">
-        <v>488</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.005644160012943988</v>
+        <v>0.005273737690881464</v>
       </c>
       <c r="M3" t="n">
-        <v>5.806195164184153</v>
+        <v>5.805502968371266</v>
       </c>
       <c r="N3" t="n">
-        <v>53.40304571541191</v>
+        <v>53.38211398160018</v>
       </c>
       <c r="O3" t="n">
-        <v>7.307738755279359</v>
+        <v>7.30630645275711</v>
       </c>
       <c r="P3" t="n">
-        <v>389.3724802825073</v>
+        <v>389.3976370144335</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22489,28 +22532,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1592860893321353</v>
+        <v>0.1555472083839098</v>
       </c>
       <c r="J4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03389292176396075</v>
+        <v>0.03235469579835448</v>
       </c>
       <c r="M4" t="n">
-        <v>5.312583382225412</v>
+        <v>5.319674491994911</v>
       </c>
       <c r="N4" t="n">
-        <v>42.57258944358075</v>
+        <v>42.68459262320813</v>
       </c>
       <c r="O4" t="n">
-        <v>6.524767386166403</v>
+        <v>6.533344673534998</v>
       </c>
       <c r="P4" t="n">
-        <v>384.540824137675</v>
+        <v>384.5782347984843</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22567,28 +22610,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1769326543485328</v>
+        <v>0.1717818299568766</v>
       </c>
       <c r="J5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03518302810079066</v>
+        <v>0.03312497445053852</v>
       </c>
       <c r="M5" t="n">
-        <v>5.937449996733357</v>
+        <v>5.953135393504366</v>
       </c>
       <c r="N5" t="n">
-        <v>50.53424910069587</v>
+        <v>50.80858104353467</v>
       </c>
       <c r="O5" t="n">
-        <v>7.108744551655789</v>
+        <v>7.128013821783363</v>
       </c>
       <c r="P5" t="n">
-        <v>385.8018258892247</v>
+        <v>385.8533642363592</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22645,28 +22688,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1673060518840783</v>
+        <v>0.1610933761115191</v>
       </c>
       <c r="J6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0323992442824117</v>
+        <v>0.02990558609410077</v>
       </c>
       <c r="M6" t="n">
-        <v>5.608144914923646</v>
+        <v>5.636212205176475</v>
       </c>
       <c r="N6" t="n">
-        <v>49.20879517703814</v>
+        <v>49.65750308630156</v>
       </c>
       <c r="O6" t="n">
-        <v>7.014898087430646</v>
+        <v>7.046808006913595</v>
       </c>
       <c r="P6" t="n">
-        <v>391.1721634704254</v>
+        <v>391.2343265371995</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22723,28 +22766,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1809618910455318</v>
+        <v>0.176223251098681</v>
       </c>
       <c r="J7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04562787229445087</v>
+        <v>0.04321565948969008</v>
       </c>
       <c r="M7" t="n">
-        <v>4.901704979970434</v>
+        <v>4.918092116021607</v>
       </c>
       <c r="N7" t="n">
-        <v>40.3199415409823</v>
+        <v>40.55712470556463</v>
       </c>
       <c r="O7" t="n">
-        <v>6.349798543338387</v>
+        <v>6.368447589920532</v>
       </c>
       <c r="P7" t="n">
-        <v>395.8282530963184</v>
+        <v>395.8756671900549</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22801,28 +22844,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08855404998200808</v>
+        <v>0.08462848733183849</v>
       </c>
       <c r="J8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01281574118140261</v>
+        <v>0.01169432077788435</v>
       </c>
       <c r="M8" t="n">
-        <v>4.628045825783796</v>
+        <v>4.637093394027032</v>
       </c>
       <c r="N8" t="n">
-        <v>35.55735616629998</v>
+        <v>35.70403266014656</v>
       </c>
       <c r="O8" t="n">
-        <v>5.962998923888883</v>
+        <v>5.975285153040527</v>
       </c>
       <c r="P8" t="n">
-        <v>389.8420481236477</v>
+        <v>389.8813266925094</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22860,7 +22903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I490"/>
+  <dimension ref="A1:I491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45885,6 +45928,53 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-34.94342826736028,173.57338484078528</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-34.94399745030411,173.57381711803563</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-34.94439059600504,173.57451764902484</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-34.94470717880102,173.57530887057933</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-34.94490584541603,173.57615129697956</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-34.944955210131994,173.5770039585972</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-34.94494854164327,173.57785191728834</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I491"/>
+  <dimension ref="A1:I493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16641,6 +16641,72 @@
       <c r="I491" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>396.07</v>
+      </c>
+      <c r="C492" t="n">
+        <v>384.78</v>
+      </c>
+      <c r="D492" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="E492" t="n">
+        <v>376.84</v>
+      </c>
+      <c r="F492" t="n">
+        <v>378.72</v>
+      </c>
+      <c r="G492" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="H492" t="n">
+        <v>381.2</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>397.15</v>
+      </c>
+      <c r="C493" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="D493" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="E493" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="F493" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="G493" t="n">
+        <v>386.84</v>
+      </c>
+      <c r="H493" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B555"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22208,6 +22274,26 @@
       </c>
       <c r="B555" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -22376,28 +22462,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2036220473045119</v>
+        <v>0.2008898352239304</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01223345460837011</v>
+        <v>0.01200576847055301</v>
       </c>
       <c r="M2" t="n">
-        <v>11.03002191486912</v>
+        <v>10.99962288299434</v>
       </c>
       <c r="N2" t="n">
-        <v>196.2543521937775</v>
+        <v>195.5090148272503</v>
       </c>
       <c r="O2" t="n">
-        <v>14.0090810617177</v>
+        <v>13.98245381995772</v>
       </c>
       <c r="P2" t="n">
-        <v>394.866475099992</v>
+        <v>394.8940199210047</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22454,28 +22540,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0694821270358887</v>
+        <v>0.06448660622818932</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K3" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005273737690881464</v>
+        <v>0.004568474393794597</v>
       </c>
       <c r="M3" t="n">
-        <v>5.805502968371266</v>
+        <v>5.803958400175366</v>
       </c>
       <c r="N3" t="n">
-        <v>53.38211398160018</v>
+        <v>53.34155306923236</v>
       </c>
       <c r="O3" t="n">
-        <v>7.30630645275711</v>
+        <v>7.303530178566551</v>
       </c>
       <c r="P3" t="n">
-        <v>389.3976370144335</v>
+        <v>389.4480041577957</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22532,28 +22618,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1555472083839098</v>
+        <v>0.1480954618264778</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03235469579835448</v>
+        <v>0.02938843474407793</v>
       </c>
       <c r="M4" t="n">
-        <v>5.319674491994911</v>
+        <v>5.333442880776603</v>
       </c>
       <c r="N4" t="n">
-        <v>42.68459262320813</v>
+        <v>42.90786519451571</v>
       </c>
       <c r="O4" t="n">
-        <v>6.533344673534998</v>
+        <v>6.550409544029725</v>
       </c>
       <c r="P4" t="n">
-        <v>384.5782347984843</v>
+        <v>384.6529972583486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22610,28 +22696,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1717818299568766</v>
+        <v>0.1614597232515045</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03312497445053852</v>
+        <v>0.02918727264333587</v>
       </c>
       <c r="M5" t="n">
-        <v>5.953135393504366</v>
+        <v>5.985484046150431</v>
       </c>
       <c r="N5" t="n">
-        <v>50.80858104353467</v>
+        <v>51.36351713059423</v>
       </c>
       <c r="O5" t="n">
-        <v>7.128013821783363</v>
+        <v>7.166834526525238</v>
       </c>
       <c r="P5" t="n">
-        <v>385.8533642363592</v>
+        <v>385.956925088044</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22688,28 +22774,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1610933761115191</v>
+        <v>0.1482095228948936</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02990558609410077</v>
+        <v>0.02504984464366844</v>
       </c>
       <c r="M6" t="n">
-        <v>5.636212205176475</v>
+        <v>5.695503668818812</v>
       </c>
       <c r="N6" t="n">
-        <v>49.65750308630156</v>
+        <v>50.64236688044519</v>
       </c>
       <c r="O6" t="n">
-        <v>7.046808006913595</v>
+        <v>7.11634505068755</v>
       </c>
       <c r="P6" t="n">
-        <v>391.2343265371995</v>
+        <v>391.3635897484387</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22766,28 +22852,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.176223251098681</v>
+        <v>0.1663220294036908</v>
       </c>
       <c r="J7" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K7" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04321565948969008</v>
+        <v>0.03834673021517465</v>
       </c>
       <c r="M7" t="n">
-        <v>4.918092116021607</v>
+        <v>4.952892531132492</v>
       </c>
       <c r="N7" t="n">
-        <v>40.55712470556463</v>
+        <v>41.09359403228979</v>
       </c>
       <c r="O7" t="n">
-        <v>6.368447589920532</v>
+        <v>6.410428537335846</v>
       </c>
       <c r="P7" t="n">
-        <v>395.8756671900549</v>
+        <v>395.9750063803478</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22844,28 +22930,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08462848733183849</v>
+        <v>0.07620014958792083</v>
       </c>
       <c r="J8" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K8" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01169432077788435</v>
+        <v>0.009446384521447304</v>
       </c>
       <c r="M8" t="n">
-        <v>4.637093394027032</v>
+        <v>4.658003761315384</v>
       </c>
       <c r="N8" t="n">
-        <v>35.70403266014656</v>
+        <v>36.06686681243026</v>
       </c>
       <c r="O8" t="n">
-        <v>5.975285153040527</v>
+        <v>6.005569649286424</v>
       </c>
       <c r="P8" t="n">
-        <v>389.8813266925094</v>
+        <v>389.9658880846903</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22903,7 +22989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I491"/>
+  <dimension ref="A1:I493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45975,6 +46061,100 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-34.94340632036765,173.5734189092963</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-34.94399676807614,173.5738178341104</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-34.94439059600504,173.57451764902484</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-34.94470701040737,173.57530894898116</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-34.94490934665856,173.57615024457937</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-34.94495746218639,173.57700383632692</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-34.94495374933028,173.5778525031671</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-34.94340031966928,173.5734282242278</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-34.94399915587399,173.57381532784865</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-34.94439203815088,173.57451674455416</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-34.9447107992645,173.57530718493973</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-34.94491669926785,173.57614803453873</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-34.94496601999313,173.57700337169996</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-34.94495958553123,173.57785315975545</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I493"/>
+  <dimension ref="A1:I496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16705,6 +16705,105 @@
         <v>380.55</v>
       </c>
       <c r="I493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>401.17</v>
+      </c>
+      <c r="C494" t="n">
+        <v>382.72</v>
+      </c>
+      <c r="D494" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="E494" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="F494" t="n">
+        <v>374.57</v>
+      </c>
+      <c r="G494" t="n">
+        <v>383.14</v>
+      </c>
+      <c r="H494" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>404.2</v>
+      </c>
+      <c r="C495" t="n">
+        <v>383.29</v>
+      </c>
+      <c r="D495" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="E495" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="G495" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="H495" t="n">
+        <v>379.79</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>408.87</v>
+      </c>
+      <c r="C496" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="D496" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="E496" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="F496" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="G496" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="H496" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="I496" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16721,7 +16820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22294,6 +22393,36 @@
       </c>
       <c r="B557" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -22462,28 +22591,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2008898352239304</v>
+        <v>0.2059735202211625</v>
       </c>
       <c r="J2" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01200576847055301</v>
+        <v>0.01275625541747116</v>
       </c>
       <c r="M2" t="n">
-        <v>10.99962288299434</v>
+        <v>10.96034293251035</v>
       </c>
       <c r="N2" t="n">
-        <v>195.5090148272503</v>
+        <v>194.5050813175246</v>
       </c>
       <c r="O2" t="n">
-        <v>13.98245381995772</v>
+        <v>13.94650785385089</v>
       </c>
       <c r="P2" t="n">
-        <v>394.8940199210047</v>
+        <v>394.842500141324</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22540,28 +22669,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06448660622818932</v>
+        <v>0.05548220692620966</v>
       </c>
       <c r="J3" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004568474393794597</v>
+        <v>0.00340295787920819</v>
       </c>
       <c r="M3" t="n">
-        <v>5.803958400175366</v>
+        <v>5.808391328025623</v>
       </c>
       <c r="N3" t="n">
-        <v>53.34155306923236</v>
+        <v>53.40445166874933</v>
       </c>
       <c r="O3" t="n">
-        <v>7.303530178566551</v>
+        <v>7.307834950842098</v>
       </c>
       <c r="P3" t="n">
-        <v>389.4480041577957</v>
+        <v>389.5391662710989</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22618,28 +22747,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1480954618264778</v>
+        <v>0.1363847994446739</v>
       </c>
       <c r="J4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02938843474407793</v>
+        <v>0.02496236756192294</v>
       </c>
       <c r="M4" t="n">
-        <v>5.333442880776603</v>
+        <v>5.356476656333744</v>
       </c>
       <c r="N4" t="n">
-        <v>42.90786519451571</v>
+        <v>43.30763945132497</v>
       </c>
       <c r="O4" t="n">
-        <v>6.550409544029725</v>
+        <v>6.580854006230876</v>
       </c>
       <c r="P4" t="n">
-        <v>384.6529972583486</v>
+        <v>384.7709796884759</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22696,28 +22825,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1614597232515045</v>
+        <v>0.1439105281020147</v>
       </c>
       <c r="J5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02918727264333587</v>
+        <v>0.02295958861763525</v>
       </c>
       <c r="M5" t="n">
-        <v>5.985484046150431</v>
+        <v>6.048178656053213</v>
       </c>
       <c r="N5" t="n">
-        <v>51.36351713059423</v>
+        <v>52.53279741004568</v>
       </c>
       <c r="O5" t="n">
-        <v>7.166834526525238</v>
+        <v>7.247951256047855</v>
       </c>
       <c r="P5" t="n">
-        <v>385.956925088044</v>
+        <v>386.1337323952727</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22774,28 +22903,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1482095228948936</v>
+        <v>0.1261890001678984</v>
       </c>
       <c r="J6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02504984464366844</v>
+        <v>0.01770216083259302</v>
       </c>
       <c r="M6" t="n">
-        <v>5.695503668818812</v>
+        <v>5.801821175463329</v>
       </c>
       <c r="N6" t="n">
-        <v>50.64236688044519</v>
+        <v>52.66921852090999</v>
       </c>
       <c r="O6" t="n">
-        <v>7.11634505068755</v>
+        <v>7.257356166050416</v>
       </c>
       <c r="P6" t="n">
-        <v>391.3635897484387</v>
+        <v>391.5854390249792</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22852,28 +22981,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1663220294036908</v>
+        <v>0.1476989255596015</v>
       </c>
       <c r="J7" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K7" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03834673021517465</v>
+        <v>0.02967900417078306</v>
       </c>
       <c r="M7" t="n">
-        <v>4.952892531132492</v>
+        <v>5.027643116049694</v>
       </c>
       <c r="N7" t="n">
-        <v>41.09359403228979</v>
+        <v>42.51260772431874</v>
       </c>
       <c r="O7" t="n">
-        <v>6.410428537335846</v>
+        <v>6.520169301814082</v>
       </c>
       <c r="P7" t="n">
-        <v>395.9750063803478</v>
+        <v>396.1626334570753</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22930,28 +23059,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07620014958792083</v>
+        <v>0.06250655251868073</v>
       </c>
       <c r="J8" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K8" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009446384521447304</v>
+        <v>0.006296999405221326</v>
       </c>
       <c r="M8" t="n">
-        <v>4.658003761315384</v>
+        <v>4.695922151115673</v>
       </c>
       <c r="N8" t="n">
-        <v>36.06686681243026</v>
+        <v>36.75115660280972</v>
       </c>
       <c r="O8" t="n">
-        <v>6.005569649286424</v>
+        <v>6.062273220732444</v>
       </c>
       <c r="P8" t="n">
-        <v>389.9658880846903</v>
+        <v>390.1038450675588</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22989,7 +23118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I493"/>
+  <dimension ref="A1:I496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46155,6 +46284,147 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-34.94337798373026,173.57346289646082</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-34.94401082197132,173.57380308296763</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-34.94440037054889,173.57451151872283</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-34.944729322565706,173.57529856073475</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-34.94494567204923,173.5761393259224</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-34.944999350398206,173.5770015620993</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-34.944973233262644,173.57785469516242</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-34.94336114842646,173.57348902999712</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-34.94400693327234,173.573807164595</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-34.944394842323305,173.57451498586104</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-34.944726038889634,173.57530008957139</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-34.944935080790856,173.5761425094354</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-34.944990432262806,173.57700204628986</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-34.94496640939693,173.57785392745885</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-34.943335200934136,173.57352930839681</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-34.94400679682676,173.57380730781</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-34.9443954031578,173.5745146341224</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-34.944725870495986,173.57530016797324</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-34.94493201720371,173.57614343028615</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-34.94499484628941,173.57700180664</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-34.94496272810097,173.57785351330304</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I496"/>
+  <dimension ref="A1:I497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16806,6 +16806,39 @@
       <c r="I496" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>419.64</v>
+      </c>
+      <c r="C497" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="D497" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="E497" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="F497" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="G497" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="H497" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22423,6 +22456,16 @@
       </c>
       <c r="B560" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -22591,28 +22634,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2059735202211625</v>
+        <v>0.2132122911820312</v>
       </c>
       <c r="J2" t="n">
+        <v>496</v>
+      </c>
+      <c r="K2" t="n">
         <v>495</v>
       </c>
-      <c r="K2" t="n">
-        <v>494</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01275625541747116</v>
+        <v>0.01366008139853581</v>
       </c>
       <c r="M2" t="n">
-        <v>10.96034293251035</v>
+        <v>10.97702567043746</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5050813175246</v>
+        <v>194.8614090305252</v>
       </c>
       <c r="O2" t="n">
-        <v>13.94650785385089</v>
+        <v>13.9592768090086</v>
       </c>
       <c r="P2" t="n">
-        <v>394.842500141324</v>
+        <v>394.7687752649435</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22669,28 +22712,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05548220692620966</v>
+        <v>0.05298283452565547</v>
       </c>
       <c r="J3" t="n">
+        <v>496</v>
+      </c>
+      <c r="K3" t="n">
         <v>495</v>
       </c>
-      <c r="K3" t="n">
-        <v>494</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00340295787920819</v>
+        <v>0.003111848048399479</v>
       </c>
       <c r="M3" t="n">
-        <v>5.808391328025623</v>
+        <v>5.807532596629296</v>
       </c>
       <c r="N3" t="n">
-        <v>53.40445166874933</v>
+        <v>53.38588806618223</v>
       </c>
       <c r="O3" t="n">
-        <v>7.307834950842098</v>
+        <v>7.306564724012389</v>
       </c>
       <c r="P3" t="n">
-        <v>389.5391662710989</v>
+        <v>389.5646216864251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22747,28 +22790,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1363847994446739</v>
+        <v>0.1333325444578769</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02496236756192294</v>
+        <v>0.02390793965260363</v>
       </c>
       <c r="M4" t="n">
-        <v>5.356476656333744</v>
+        <v>5.360011060901379</v>
       </c>
       <c r="N4" t="n">
-        <v>43.30763945132497</v>
+        <v>43.35470495268959</v>
       </c>
       <c r="O4" t="n">
-        <v>6.580854006230876</v>
+        <v>6.584428976964486</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7709796884759</v>
+        <v>384.8019151605314</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22825,28 +22868,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1439105281020147</v>
+        <v>0.1394448453089321</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02295958861763525</v>
+        <v>0.02155879815687212</v>
       </c>
       <c r="M5" t="n">
-        <v>6.048178656053213</v>
+        <v>6.061546248201959</v>
       </c>
       <c r="N5" t="n">
-        <v>52.53279741004568</v>
+        <v>52.71453589214848</v>
       </c>
       <c r="O5" t="n">
-        <v>7.247951256047855</v>
+        <v>7.260477662809002</v>
       </c>
       <c r="P5" t="n">
-        <v>386.1337323952727</v>
+        <v>386.1789933599861</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22903,28 +22946,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1261890001678984</v>
+        <v>0.1199598106426194</v>
       </c>
       <c r="J6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01770216083259302</v>
+        <v>0.01592338341758803</v>
       </c>
       <c r="M6" t="n">
-        <v>5.801821175463329</v>
+        <v>5.829757465792915</v>
       </c>
       <c r="N6" t="n">
-        <v>52.66921852090999</v>
+        <v>53.12272865038985</v>
       </c>
       <c r="O6" t="n">
-        <v>7.257356166050416</v>
+        <v>7.288534053593345</v>
       </c>
       <c r="P6" t="n">
-        <v>391.5854390249792</v>
+        <v>391.6485736317933</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22981,28 +23024,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1476989255596015</v>
+        <v>0.1414418693835627</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02967900417078306</v>
+        <v>0.02704459210172039</v>
       </c>
       <c r="M7" t="n">
-        <v>5.027643116049694</v>
+        <v>5.052798965616081</v>
       </c>
       <c r="N7" t="n">
-        <v>42.51260772431874</v>
+        <v>42.99161377816167</v>
       </c>
       <c r="O7" t="n">
-        <v>6.520169301814082</v>
+        <v>6.556799049701132</v>
       </c>
       <c r="P7" t="n">
-        <v>396.1626334570753</v>
+        <v>396.2260505003174</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23059,28 +23102,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06250655251868073</v>
+        <v>0.05795660494897712</v>
       </c>
       <c r="J8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006296999405221326</v>
+        <v>0.005397030021791593</v>
       </c>
       <c r="M8" t="n">
-        <v>4.695922151115673</v>
+        <v>4.709379876805515</v>
       </c>
       <c r="N8" t="n">
-        <v>36.75115660280972</v>
+        <v>36.97567094937411</v>
       </c>
       <c r="O8" t="n">
-        <v>6.062273220732444</v>
+        <v>6.080762365803658</v>
       </c>
       <c r="P8" t="n">
-        <v>390.1038450675588</v>
+        <v>390.1499600797401</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23118,7 +23161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I496"/>
+  <dimension ref="A1:I497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46425,6 +46468,53 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-34.94327536052134,173.57362219874184</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-34.94399976987914,173.57381468338133</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-34.94437953955345,173.57452458329914</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-34.944697411969166,173.57531341788547</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-34.94491363568064,173.57614895538904</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-34.94499790908338,173.5770016403523</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-34.9449684745142,173.57785415979018</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>404.2</v>
+        <v>401.17</v>
       </c>
       <c r="C495" t="n">
         <v>383.29</v>
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>408.87</v>
+        <v>403.15</v>
       </c>
       <c r="C496" t="n">
         <v>383.31</v>
@@ -16816,7 +16816,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>419.64</v>
+        <v>414.36</v>
       </c>
       <c r="C497" t="n">
         <v>384.34</v>
@@ -16839,6 +16839,138 @@
       <c r="I497" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="C498" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="D498" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="E498" t="n">
+        <v>379.15</v>
+      </c>
+      <c r="F498" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="G498" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="H498" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>420.9</v>
+      </c>
+      <c r="C499" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="D499" t="n">
+        <v>381.17</v>
+      </c>
+      <c r="E499" t="n">
+        <v>379.81</v>
+      </c>
+      <c r="F499" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="G499" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="H499" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>417.17</v>
+      </c>
+      <c r="C500" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="D500" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="E500" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="F500" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="G500" t="n">
+        <v>386.09</v>
+      </c>
+      <c r="H500" t="n">
+        <v>380.69</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>408.23</v>
+      </c>
+      <c r="C501" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="D501" t="n">
+        <v>380.97</v>
+      </c>
+      <c r="E501" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="F501" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="G501" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="H501" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B561"/>
+  <dimension ref="A1:B565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22466,6 +22598,46 @@
       </c>
       <c r="B561" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -22634,28 +22806,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2132122911820312</v>
+        <v>0.2322422370977151</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01366008139853581</v>
+        <v>0.01628153061237869</v>
       </c>
       <c r="M2" t="n">
-        <v>10.97702567043746</v>
+        <v>10.98914081527117</v>
       </c>
       <c r="N2" t="n">
-        <v>194.8614090305252</v>
+        <v>195.1156707867057</v>
       </c>
       <c r="O2" t="n">
-        <v>13.9592768090086</v>
+        <v>13.96838110829976</v>
       </c>
       <c r="P2" t="n">
-        <v>394.7687752649435</v>
+        <v>394.5735298922759</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22712,28 +22884,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05298283452565547</v>
+        <v>0.04441418381643014</v>
       </c>
       <c r="J3" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003111848048399479</v>
+        <v>0.002214255725878522</v>
       </c>
       <c r="M3" t="n">
-        <v>5.807532596629296</v>
+        <v>5.797573692598779</v>
       </c>
       <c r="N3" t="n">
-        <v>53.38588806618223</v>
+        <v>53.22149051714529</v>
       </c>
       <c r="O3" t="n">
-        <v>7.306564724012389</v>
+        <v>7.295306060553271</v>
       </c>
       <c r="P3" t="n">
-        <v>389.5646216864251</v>
+        <v>389.6523785592699</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22790,28 +22962,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1333325444578769</v>
+        <v>0.1226687633640021</v>
       </c>
       <c r="J4" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K4" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02390793965260363</v>
+        <v>0.02045148313240286</v>
       </c>
       <c r="M4" t="n">
-        <v>5.360011060901379</v>
+        <v>5.367585931617981</v>
       </c>
       <c r="N4" t="n">
-        <v>43.35470495268959</v>
+        <v>43.41894794568112</v>
       </c>
       <c r="O4" t="n">
-        <v>6.584428976964486</v>
+        <v>6.58930557385838</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8019151605314</v>
+        <v>384.9105963280489</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22868,28 +23040,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1394448453089321</v>
+        <v>0.1247942304420308</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02155879815687212</v>
+        <v>0.01737128833277035</v>
       </c>
       <c r="M5" t="n">
-        <v>6.061546248201959</v>
+        <v>6.095651282695359</v>
       </c>
       <c r="N5" t="n">
-        <v>52.71453589214848</v>
+        <v>53.07091974392347</v>
       </c>
       <c r="O5" t="n">
-        <v>7.260477662809002</v>
+        <v>7.284979048969425</v>
       </c>
       <c r="P5" t="n">
-        <v>386.1789933599861</v>
+        <v>386.3282975220405</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22946,28 +23118,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1199598106426194</v>
+        <v>0.1009381536048635</v>
       </c>
       <c r="J6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01592338341758803</v>
+        <v>0.01123657271721989</v>
       </c>
       <c r="M6" t="n">
-        <v>5.829757465792915</v>
+        <v>5.903939482091533</v>
       </c>
       <c r="N6" t="n">
-        <v>53.12272865038985</v>
+        <v>54.01065185220103</v>
       </c>
       <c r="O6" t="n">
-        <v>7.288534053593345</v>
+        <v>7.349193959353708</v>
       </c>
       <c r="P6" t="n">
-        <v>391.6485736317933</v>
+        <v>391.8424244281958</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23024,28 +23196,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1414418693835627</v>
+        <v>0.1197937939521482</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02704459210172039</v>
+        <v>0.01911808132288129</v>
       </c>
       <c r="M7" t="n">
-        <v>5.052798965616081</v>
+        <v>5.1369376401101</v>
       </c>
       <c r="N7" t="n">
-        <v>42.99161377816167</v>
+        <v>44.35588432384697</v>
       </c>
       <c r="O7" t="n">
-        <v>6.556799049701132</v>
+        <v>6.66002134559995</v>
       </c>
       <c r="P7" t="n">
-        <v>396.2260505003174</v>
+        <v>396.4466538222992</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23102,28 +23274,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05795660494897712</v>
+        <v>0.0412502700620558</v>
       </c>
       <c r="J8" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K8" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005397030021791593</v>
+        <v>0.002712397569877067</v>
       </c>
       <c r="M8" t="n">
-        <v>4.709379876805515</v>
+        <v>4.758116058384052</v>
       </c>
       <c r="N8" t="n">
-        <v>36.97567094937411</v>
+        <v>37.69040852935033</v>
       </c>
       <c r="O8" t="n">
-        <v>6.080762365803658</v>
+        <v>6.139251463277126</v>
       </c>
       <c r="P8" t="n">
-        <v>390.1499600797401</v>
+        <v>390.3202159265054</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23161,7 +23333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46382,7 +46554,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>-34.94336114842646,173.57348902999712</t>
+          <t>-34.94337798373026,173.57346289646082</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -46429,7 +46601,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>-34.943335200934136,173.57352930839681</t>
+          <t>-34.94336698244327,173.5734799738224</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -46476,7 +46648,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>-34.94327536052134,173.57362219874184</t>
+          <t>-34.94330469733417,173.57357665920244</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -46512,6 +46684,194 @@
       <c r="I497" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-34.94326835968852,173.57363306612714</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-34.94399424383264,173.57382048358699</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-34.94437409144671,173.57452800018726</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-34.94468756094031,173.57531800439145</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-34.944889827231314,173.5761561117092</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-34.94499520661812,173.57700178707674</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-34.94496820515107,173.5778541294861</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-34.94326835968852,173.57363306612714</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-34.943991105583876,173.5738237775306</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-34.94437184810863,173.57452940714103</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-34.94468200394959,173.57532059165075</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-34.944880811531625,173.57615882163822</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-34.944988180208405,173.57700216856017</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-34.94496344640262,173.57785359411392</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-34.94328908437339,173.57360089521137</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-34.94399397094144,173.57382077001688</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-34.94437008548582,173.5745305126047</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-34.9446800674225,173.57532149327136</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-34.94488510055381,173.57615753244875</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-34.944972776156334,173.5770030048891</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-34.94495832850333,173.5778530183364</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-34.94333875690817,173.57352378844632</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-34.94399669985335,173.57381790571787</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-34.94437345049298,173.57452840217405</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-34.944674173644394,173.57532423733375</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-34.944869957679494,173.57616208407626</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-34.94496439851396,173.57700345973456</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-34.944956263386075,173.57785278600514</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16969,6 +16969,138 @@
         <v>380.92</v>
       </c>
       <c r="I501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>403.59</v>
+      </c>
+      <c r="C502" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="D502" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="E502" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="F502" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="G502" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="H502" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>400.27</v>
+      </c>
+      <c r="C503" t="n">
+        <v>383.62</v>
+      </c>
+      <c r="D503" t="n">
+        <v>379.44</v>
+      </c>
+      <c r="E503" t="n">
+        <v>379.22</v>
+      </c>
+      <c r="F503" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="G503" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="H503" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="C504" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="D504" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="E504" t="n">
+        <v>379.43</v>
+      </c>
+      <c r="F504" t="n">
+        <v>383.71</v>
+      </c>
+      <c r="G504" t="n">
+        <v>388.3</v>
+      </c>
+      <c r="H504" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>389.47</v>
+      </c>
+      <c r="C505" t="n">
+        <v>383.25</v>
+      </c>
+      <c r="D505" t="n">
+        <v>378.08</v>
+      </c>
+      <c r="E505" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="F505" t="n">
+        <v>384.36</v>
+      </c>
+      <c r="G505" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="H505" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="I505" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16985,7 +17117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B565"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22638,6 +22770,46 @@
       </c>
       <c r="B565" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -22806,28 +22978,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2322422370977151</v>
+        <v>0.2265403577779356</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01628153061237869</v>
+        <v>0.01572613613752272</v>
       </c>
       <c r="M2" t="n">
-        <v>10.98914081527117</v>
+        <v>10.94446758402426</v>
       </c>
       <c r="N2" t="n">
-        <v>195.1156707867057</v>
+        <v>193.9193877815655</v>
       </c>
       <c r="O2" t="n">
-        <v>13.96838110829976</v>
+        <v>13.92549416651221</v>
       </c>
       <c r="P2" t="n">
-        <v>394.5735298922759</v>
+        <v>394.6322110974625</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22884,28 +23056,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04441418381643014</v>
+        <v>0.0339532789590901</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002214255725878522</v>
+        <v>0.001306498302763526</v>
       </c>
       <c r="M3" t="n">
-        <v>5.797573692598779</v>
+        <v>5.795949173618185</v>
       </c>
       <c r="N3" t="n">
-        <v>53.22149051714529</v>
+        <v>53.2013879345585</v>
       </c>
       <c r="O3" t="n">
-        <v>7.295306060553271</v>
+        <v>7.293928155291804</v>
       </c>
       <c r="P3" t="n">
-        <v>389.6523785592699</v>
+        <v>389.7599077286963</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22962,28 +23134,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1226687633640021</v>
+        <v>0.1094704195545899</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02045148313240286</v>
+        <v>0.01637570546558476</v>
       </c>
       <c r="M4" t="n">
-        <v>5.367585931617981</v>
+        <v>5.387257696333891</v>
       </c>
       <c r="N4" t="n">
-        <v>43.41894794568112</v>
+        <v>43.72443848524771</v>
       </c>
       <c r="O4" t="n">
-        <v>6.58930557385838</v>
+        <v>6.612445726450064</v>
       </c>
       <c r="P4" t="n">
-        <v>384.9105963280489</v>
+        <v>385.045617318257</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23040,28 +23212,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1247942304420308</v>
+        <v>0.1102166446509611</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01737128833277035</v>
+        <v>0.01362014439457659</v>
       </c>
       <c r="M5" t="n">
-        <v>6.095651282695359</v>
+        <v>6.130320128127802</v>
       </c>
       <c r="N5" t="n">
-        <v>53.07091974392347</v>
+        <v>53.43899734795333</v>
       </c>
       <c r="O5" t="n">
-        <v>7.284979048969425</v>
+        <v>7.310198174328336</v>
       </c>
       <c r="P5" t="n">
-        <v>386.3282975220405</v>
+        <v>386.4774186989718</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23118,28 +23290,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1009381536048635</v>
+        <v>0.08473242860561266</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01123657271721989</v>
+        <v>0.007929760469047364</v>
       </c>
       <c r="M6" t="n">
-        <v>5.903939482091533</v>
+        <v>5.961222915655994</v>
       </c>
       <c r="N6" t="n">
-        <v>54.01065185220103</v>
+        <v>54.56109892123861</v>
       </c>
       <c r="O6" t="n">
-        <v>7.349193959353708</v>
+        <v>7.386548512075082</v>
       </c>
       <c r="P6" t="n">
-        <v>391.8424244281958</v>
+        <v>392.0081901136009</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23196,28 +23368,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1197937939521482</v>
+        <v>0.1027512386076118</v>
       </c>
       <c r="J7" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01911808132288129</v>
+        <v>0.01402379644409069</v>
       </c>
       <c r="M7" t="n">
-        <v>5.1369376401101</v>
+        <v>5.197589607699689</v>
       </c>
       <c r="N7" t="n">
-        <v>44.35588432384697</v>
+        <v>45.0896031594559</v>
       </c>
       <c r="O7" t="n">
-        <v>6.66002134559995</v>
+        <v>6.714879236401493</v>
       </c>
       <c r="P7" t="n">
-        <v>396.4466538222992</v>
+        <v>396.6209765256945</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23274,28 +23446,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0412502700620558</v>
+        <v>0.02795149447617926</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002712397569877067</v>
+        <v>0.001245567087701738</v>
       </c>
       <c r="M8" t="n">
-        <v>4.758116058384052</v>
+        <v>4.792427738000538</v>
       </c>
       <c r="N8" t="n">
-        <v>37.69040852935033</v>
+        <v>38.05424497103047</v>
       </c>
       <c r="O8" t="n">
-        <v>6.139251463277126</v>
+        <v>6.168812282038616</v>
       </c>
       <c r="P8" t="n">
-        <v>390.3202159265054</v>
+        <v>390.456243924443</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23333,7 +23505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46875,6 +47047,194 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-34.94336453771249,173.57348376879102</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-34.94400188478575,173.5738124635493</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-34.94438178289149,173.57452317634508</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-34.94467998322568,173.57532153247226</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-34.94487573472983,173.5761603476174</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-34.944966110075306,173.57700336680915</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-34.944956622536914,173.57785282641058</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-34.943382984314475,173.57345513402223</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-34.94400468192024,173.57380952764228</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-34.94438570873301,173.57452071417532</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-34.9446869715625,173.57531827879777</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-34.944874684357046,173.57616066333722</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-34.94496421834962,173.57700346951614</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-34.94494665610143,173.57785170515984</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-34.94341682158809,173.5734026081629</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-34.94400440902907,173.57380981407223</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-34.94439075624347,173.5745175485281</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-34.9446852034291,173.57531910201666</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-34.94486566865723,173.57616337326525</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-34.94495286799541,173.57700408575823</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-34.94494037096191,173.57785099806495</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-34.94344299128676,173.5733619846854</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-34.9440072061635,173.57380687816504</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-34.94439660494597,173.57451388039672</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-34.94468360368934,173.57531984683374</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-34.94485997913791,173.57616508341374</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-34.944944220106464,173.5770045552759</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-34.94493471433634,173.57785036167965</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0034/nzd0034.xlsx
+++ b/data/nzd0034/nzd0034.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17101,6 +17101,171 @@
         <v>383.32</v>
       </c>
       <c r="I505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>387.42</v>
+      </c>
+      <c r="C506" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="D506" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="E506" t="n">
+        <v>379.65</v>
+      </c>
+      <c r="F506" t="n">
+        <v>384.41</v>
+      </c>
+      <c r="G506" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="H506" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="C507" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="D507" t="n">
+        <v>379</v>
+      </c>
+      <c r="E507" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="F507" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="G507" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="H507" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="C508" t="n">
+        <v>383.2</v>
+      </c>
+      <c r="D508" t="n">
+        <v>379.6</v>
+      </c>
+      <c r="E508" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="F508" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="G508" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="H508" t="n">
+        <v>383.83</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>378</v>
+      </c>
+      <c r="C509" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="D509" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="E509" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="F509" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="G509" t="n">
+        <v>390.41</v>
+      </c>
+      <c r="H509" t="n">
+        <v>384.45</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="C510" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="D510" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="E510" t="n">
+        <v>380.77</v>
+      </c>
+      <c r="F510" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="G510" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="H510" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="I510" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17117,7 +17282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22810,6 +22975,56 @@
       </c>
       <c r="B569" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -22978,28 +23193,28 @@
         <v>0.1907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2265403577779356</v>
+        <v>0.1921482480149379</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01572613613752272</v>
+        <v>0.01137457131930486</v>
       </c>
       <c r="M2" t="n">
-        <v>10.94446758402426</v>
+        <v>11.0252004988353</v>
       </c>
       <c r="N2" t="n">
-        <v>193.9193877815655</v>
+        <v>195.6973708591891</v>
       </c>
       <c r="O2" t="n">
-        <v>13.92549416651221</v>
+        <v>13.9891876411459</v>
       </c>
       <c r="P2" t="n">
-        <v>394.6322110974625</v>
+        <v>394.9874121322387</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23056,28 +23271,28 @@
         <v>0.118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0339532789590901</v>
+        <v>0.02058542097362856</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001306498302763526</v>
+        <v>0.0004853609106804102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.795949173618185</v>
+        <v>5.795425621615403</v>
       </c>
       <c r="N3" t="n">
-        <v>53.2013879345585</v>
+        <v>53.21808739615205</v>
       </c>
       <c r="O3" t="n">
-        <v>7.293928155291804</v>
+        <v>7.29507281637079</v>
       </c>
       <c r="P3" t="n">
-        <v>389.7599077286963</v>
+        <v>389.8979535596885</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23134,28 +23349,28 @@
         <v>0.1162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1094704195545899</v>
+        <v>0.09392024127201945</v>
       </c>
       <c r="J4" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01637570546558476</v>
+        <v>0.01214230977101294</v>
       </c>
       <c r="M4" t="n">
-        <v>5.387257696333891</v>
+        <v>5.408814522145562</v>
       </c>
       <c r="N4" t="n">
-        <v>43.72443848524771</v>
+        <v>44.03310150412152</v>
       </c>
       <c r="O4" t="n">
-        <v>6.612445726450064</v>
+        <v>6.635744231367083</v>
       </c>
       <c r="P4" t="n">
-        <v>385.045617318257</v>
+        <v>385.2054275209953</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23212,28 +23427,28 @@
         <v>0.0878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1102166446509611</v>
+        <v>0.09347127851198973</v>
       </c>
       <c r="J5" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K5" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01362014439457659</v>
+        <v>0.009871104405382858</v>
       </c>
       <c r="M5" t="n">
-        <v>6.130320128127802</v>
+        <v>6.164971435078875</v>
       </c>
       <c r="N5" t="n">
-        <v>53.43899734795333</v>
+        <v>53.77125293523674</v>
       </c>
       <c r="O5" t="n">
-        <v>7.310198174328336</v>
+        <v>7.332888444210558</v>
       </c>
       <c r="P5" t="n">
-        <v>386.4774186989718</v>
+        <v>386.6495095308521</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23290,28 +23505,28 @@
         <v>0.06710000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08473242860561266</v>
+        <v>0.06811323052309259</v>
       </c>
       <c r="J6" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007929760469047364</v>
+        <v>0.005161248691364917</v>
       </c>
       <c r="M6" t="n">
-        <v>5.961222915655994</v>
+        <v>6.009408967349581</v>
       </c>
       <c r="N6" t="n">
-        <v>54.56109892123861</v>
+        <v>54.86920478031136</v>
       </c>
       <c r="O6" t="n">
-        <v>7.386548512075082</v>
+        <v>7.407375026303945</v>
       </c>
       <c r="P6" t="n">
-        <v>392.0081901136009</v>
+        <v>392.1789838484265</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23368,28 +23583,28 @@
         <v>0.08649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1027512386076118</v>
+        <v>0.08603182523902264</v>
       </c>
       <c r="J7" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K7" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01402379644409069</v>
+        <v>0.009881345995545132</v>
       </c>
       <c r="M7" t="n">
-        <v>5.197589607699689</v>
+        <v>5.246629497369252</v>
       </c>
       <c r="N7" t="n">
-        <v>45.0896031594559</v>
+        <v>45.5048000807549</v>
       </c>
       <c r="O7" t="n">
-        <v>6.714879236401493</v>
+        <v>6.745724577890421</v>
       </c>
       <c r="P7" t="n">
-        <v>396.6209765256945</v>
+        <v>396.7927966119701</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23446,28 +23661,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02795149447617926</v>
+        <v>0.01436272253326647</v>
       </c>
       <c r="J8" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="K8" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001245567087701738</v>
+        <v>0.0003307617865988544</v>
       </c>
       <c r="M8" t="n">
-        <v>4.792427738000538</v>
+        <v>4.819568889815709</v>
       </c>
       <c r="N8" t="n">
-        <v>38.05424497103047</v>
+        <v>38.25448334140854</v>
       </c>
       <c r="O8" t="n">
-        <v>6.168812282038616</v>
+        <v>6.185020884476344</v>
       </c>
       <c r="P8" t="n">
-        <v>390.456243924443</v>
+        <v>390.5958845527433</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -23505,7 +23720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I505"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47235,6 +47450,241 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-34.9434543814911,173.57334430354587</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-34.944006182821646,173.57380795227743</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-34.94439131707797,173.5745171967895</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-34.94468335109885,173.57531996443643</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-34.94485954148258,173.5761652149636</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-34.94494367961342,173.57700458462077</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-34.94494755397849,173.5778518061734</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>-34.943486774107086,173.57329402008332</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>-34.944009184624406,173.57380480154762</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>-34.944389233978434,173.57451850324713</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-34.94468562441324,173.57531890601217</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>-34.94485901629617,173.57616537282345</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>-34.944944220106464,173.5770045552759</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-34.94493965266025,173.5778509172541</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>-34.943486774107086,173.57329402008332</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>-34.94400754727745,173.57380652012756</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>-34.944384426825586,173.57452151814914</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-34.94468124617813,173.57532094445884</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>-34.944856040239905,173.5761662673625</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-34.94494259862729,173.57700464331046</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-34.944930135163254,173.57784984651065</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>-34.943506720836375,173.5732630564906</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>-34.94400829772813,173.5738057324451</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>-34.9443856286138,173.57452076442368</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-34.94467914125738,173.5753219244812</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>-34.94485306418361,173.57616716190154</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-34.94493386065617,173.5770051177188</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>-34.94492456832538,173.57784922022682</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-34.94350499841717,173.5732657302276</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-34.944008161282575,173.5738058756601</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-34.944387791832575,173.57451940771776</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-34.944673921053905,173.5753243549364</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-34.94484921281664,173.5761683195402</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-34.94492665408203,173.5770055089834</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-34.9449225032081,173.57784898789578</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
